--- a/examples/position-tags/岗位清单.xlsx
+++ b/examples/position-tags/岗位清单.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -74,13 +75,13 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,12 +452,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/examples/position-tags/岗位清单.xlsx
+++ b/examples/position-tags/岗位清单.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -458,6 +458,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,6 +494,11 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>职能</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>显示名</t>
         </is>
       </c>
@@ -523,6 +529,7 @@
       </c>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -554,6 +561,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -583,6 +591,7 @@
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -608,6 +617,7 @@
       </c>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -631,6 +641,7 @@
       </c>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -658,6 +669,7 @@
       </c>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -681,6 +693,7 @@
       </c>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -708,6 +721,7 @@
       </c>
       <c r="F9" s="2" t="n"/>
       <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
